--- a/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:04</t>
+    <t xml:space="preserve">2026-09-09 22:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:00</t>
+    <t xml:space="preserve">2026-09-17 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1115472.5</v>
+        <v>1207930.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1132728.25</v>
+        <v>1115472.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1207930.88</v>
+        <v>1132728.25</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>981782.56</v>
+        <v>1075311.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1115472.5</v>
+        <v>1207930.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1175327.38</v>
+        <v>1283341.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>994591.25</v>
+        <v>981782.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1132728.25</v>
+        <v>1115472.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1204223.12</v>
+        <v>1175327.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1075311.5</v>
+        <v>994591.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1207930.88</v>
+        <v>1132728.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1283341.88</v>
+        <v>1204223.12</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:33</t>
+    <t xml:space="preserve">2026-09-25 21:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,7 +527,7 @@
         <v>893324.81</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>121892.13</v>
+        <v>121892.12</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>13.64</v>
@@ -550,7 +550,7 @@
         <v>996545.44</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>98566.68</v>
+        <v>98566.69</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>9.89</v>
@@ -688,7 +688,7 @@
         <v>1004421.25</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>133544.37</v>
+        <v>133544.38</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>13.3</v>
@@ -734,7 +734,7 @@
         <v>995126.69</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>127243.93</v>
+        <v>127243.94</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>12.79</v>
@@ -780,7 +780,7 @@
         <v>1035679.25</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>131239.37</v>
+        <v>131239.38</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>12.67</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -534,7 +534,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1115472</v>
+        <v>1115473</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>981783</v>
@@ -674,7 +674,7 @@
         <v>1122371</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1208370</v>
+        <v>1208371</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>-7.1</v>
@@ -699,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1127592</v>
+        <v>1127593</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1137966</v>
